--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-observation-habitus-mode-de-vie.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-observation-habitus-mode-de-vie.xlsx
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>FR - Habitus / Mode de vie</t>
+    <t>Observation - Fr Habitus / Mode de vie</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-25T15:49:50+00:00</t>
+    <t>2025-09-03T12:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-observation-habitus-mode-de-vie.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-observation-habitus-mode-de-vie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-03T12:41:15+00:00</t>
+    <t>2025-09-04T10:23:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil Observation décrivant les habitudes de vie du patient (Habitus / Mode de vie), dérivé de FrSimpleObservation.</t>
+    <t>Profil Observation décrivant les habitudes de vie du patient (Habitus / Mode de vie).</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -925,10 +925,10 @@
 </t>
   </si>
   <si>
-    <t>Qualifier du code</t>
-  </si>
-  <si>
-    <t>An Extension</t>
+    <t>Extension - Qualifier du code</t>
+  </si>
+  <si>
+    <t>Extension permettant d’associer à un code une précision (qualifier).</t>
   </si>
   <si>
     <t>Observation.code.coding.system</t>
